--- a/output/pdf_financials_xlsx/TEX.xlsx
+++ b/output/pdf_financials_xlsx/TEX.xlsx
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0468</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.562146</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.671007</v>
       </c>
     </row>
     <row r="93">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>2.176045</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>5.13949</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.468009</v>
       </c>
     </row>
     <row r="119">
@@ -2947,7 +2947,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>0.0468</v>
       </c>
@@ -3098,7 +3102,11 @@
           <t>Shares issued for acquisition costs included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>2.176045</v>
       </c>

--- a/output/pdf_financials_xlsx/TEX.xlsx
+++ b/output/pdf_financials_xlsx/TEX.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.604316</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.220981</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.604316</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.220981</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="37">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/TEX.xlsx
+++ b/output/pdf_financials_xlsx/TEX.xlsx
@@ -3836,7 +3836,11 @@
           <t>Flow-through units issued in private placement 846,929 614,024 105,866</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -3898,7 +3902,11 @@
           <t>Charity flow-through units issued in private placement 700,000 595,000 17,500</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4150,7 +4158,11 @@
           <t>Units issued in private placement 1,339,999 569,500 100,500</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
